--- a/results/reliability_eval/Llama-3-8B_P108_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P108_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.661578909370939</v>
+        <v>0.5212490028490029</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6001558774225872</v>
+        <v>0.3345881551062938</v>
       </c>
       <c r="C2" t="n">
-        <v>0.661578909370939</v>
+        <v>0.5212490028490029</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6001558774225872</v>
+        <v>0.3345881551062938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3387820667083794</v>
+        <v>0.4726131054131054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3981041421677135</v>
+        <v>0.3168719267908566</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9973448203943464</v>
+        <v>0.9920569800569801</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9961937278607167</v>
+        <v>0.9811540832721586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.474</v>
+        <v>0.325</v>
       </c>
     </row>
   </sheetData>
